--- a/src/evaluation/data/processed/RES_policy_maker_model.xlsx
+++ b/src/evaluation/data/processed/RES_policy_maker_model.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.466</v>
+        <v>17.468</v>
       </c>
       <c r="C2" t="n">
         <v>12.08</v>
@@ -481,7 +481,7 @@
         <v>28.85</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8332063975628333</v>
+        <v>0.8358858007184723</v>
       </c>
       <c r="F2" t="n">
         <v>0.2890756302521008</v>
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.714</v>
+        <v>8.625999999999999</v>
       </c>
       <c r="C3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>13.124</v>
+        <v>12.764</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -531,13 +531,13 @@
         <v>23.792</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3204493526275704</v>
+        <v>0.3265267536396295</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6783670354826402</v>
+        <v>0.6855650876538605</v>
       </c>
     </row>
     <row r="5">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.078</v>
+        <v>14.1</v>
       </c>
       <c r="C5" t="n">
         <v>15.68</v>
@@ -556,13 +556,13 @@
         <v>25.296</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5106626047220106</v>
+        <v>0.5174891283796559</v>
       </c>
       <c r="F5" t="n">
         <v>0.5915966386554622</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7740048327610325</v>
+        <v>0.7790625388536614</v>
       </c>
     </row>
     <row r="6">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.218</v>
+        <v>19.204</v>
       </c>
       <c r="C6" t="n">
         <v>20.54</v>
       </c>
       <c r="D6" t="n">
-        <v>25.286</v>
+        <v>25.23</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -587,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7733689431514691</v>
+        <v>0.7749595921919683</v>
       </c>
     </row>
     <row r="7">
@@ -606,13 +606,13 @@
         <v>24.446</v>
       </c>
       <c r="E7" t="n">
-        <v>0.972962680883473</v>
+        <v>0.9744753261486103</v>
       </c>
       <c r="F7" t="n">
         <v>0.7663865546218489</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7199542159481116</v>
+        <v>0.7262215591197316</v>
       </c>
     </row>
   </sheetData>
